--- a/compare/output/dscale_Elec_downscaled_SSP245.xlsx
+++ b/compare/output/dscale_Elec_downscaled_SSP245.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3959.374505</v>
+        <v>3959.789664</v>
       </c>
       <c r="F2" t="n">
-        <v>9556.118543</v>
+        <v>9558.704325000001</v>
       </c>
       <c r="G2" t="n">
-        <v>18015.934892</v>
+        <v>18025.988095</v>
       </c>
       <c r="H2" t="n">
-        <v>30182.212355</v>
+        <v>30217.205</v>
       </c>
       <c r="I2" t="n">
-        <v>46123.492501</v>
+        <v>46262.577853</v>
       </c>
       <c r="J2" t="n">
         <v>20330.076194</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>337.518697</v>
+        <v>337.527033</v>
       </c>
       <c r="F3" t="n">
-        <v>729.2957</v>
+        <v>729.3448</v>
       </c>
       <c r="G3" t="n">
-        <v>1290.329112</v>
+        <v>1290.50842</v>
       </c>
       <c r="H3" t="n">
-        <v>2114.370388</v>
+        <v>2114.986747</v>
       </c>
       <c r="I3" t="n">
-        <v>3269.212118</v>
+        <v>3271.704781</v>
       </c>
       <c r="J3" t="n">
         <v>4248.060213</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>397.727313</v>
+        <v>397.654014</v>
       </c>
       <c r="F4" t="n">
-        <v>760.8795</v>
+        <v>760.541572</v>
       </c>
       <c r="G4" t="n">
-        <v>1160.500347</v>
+        <v>1159.504534</v>
       </c>
       <c r="H4" t="n">
-        <v>1705.691806</v>
+        <v>1702.819724</v>
       </c>
       <c r="I4" t="n">
-        <v>2445.452526</v>
+        <v>2435.262063</v>
       </c>
       <c r="J4" t="n">
         <v>6971.552667</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1044.184403</v>
+        <v>1044.146701</v>
       </c>
       <c r="F5" t="n">
-        <v>2944.013543</v>
+        <v>2943.662469</v>
       </c>
       <c r="G5" t="n">
-        <v>7031.950486</v>
+        <v>7029.647352</v>
       </c>
       <c r="H5" t="n">
-        <v>14342.099477</v>
+        <v>14330.644152</v>
       </c>
       <c r="I5" t="n">
-        <v>25265.781647</v>
+        <v>25209.675979</v>
       </c>
       <c r="J5" t="n">
         <v>63981.775644</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38166.858743</v>
+        <v>38167.947719</v>
       </c>
       <c r="F6" t="n">
-        <v>90846.699762</v>
+        <v>90853.079214</v>
       </c>
       <c r="G6" t="n">
-        <v>155708.729132</v>
+        <v>155732.708121</v>
       </c>
       <c r="H6" t="n">
-        <v>243175.568927</v>
+        <v>243259.477615</v>
       </c>
       <c r="I6" t="n">
-        <v>362365.211424</v>
+        <v>362706.540828</v>
       </c>
       <c r="J6" t="n">
         <v>423714.457899</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>35545.012481</v>
+        <v>35546.444834</v>
       </c>
       <c r="F7" t="n">
-        <v>89458.656776</v>
+        <v>89467.307965</v>
       </c>
       <c r="G7" t="n">
-        <v>182754.062994</v>
+        <v>182786.71635</v>
       </c>
       <c r="H7" t="n">
-        <v>336182.178978</v>
+        <v>336295.59202</v>
       </c>
       <c r="I7" t="n">
-        <v>567534.014626</v>
+        <v>567992.8035029999</v>
       </c>
       <c r="J7" t="n">
         <v>774175.608351</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7724.768918</v>
+        <v>7724.913041</v>
       </c>
       <c r="F8" t="n">
-        <v>18326.408351</v>
+        <v>18327.255847</v>
       </c>
       <c r="G8" t="n">
-        <v>34544.975698</v>
+        <v>34548.065111</v>
       </c>
       <c r="H8" t="n">
-        <v>58905.00619</v>
+        <v>58915.884452</v>
       </c>
       <c r="I8" t="n">
-        <v>92948.717741</v>
+        <v>92994.33298399999</v>
       </c>
       <c r="J8" t="n">
         <v>127988.235923</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10940.948935</v>
+        <v>10941.176043</v>
       </c>
       <c r="F9" t="n">
-        <v>20341.083001</v>
+        <v>20342.395724</v>
       </c>
       <c r="G9" t="n">
-        <v>29360.769945</v>
+        <v>29365.447028</v>
       </c>
       <c r="H9" t="n">
-        <v>40199.253288</v>
+        <v>40214.467205</v>
       </c>
       <c r="I9" t="n">
-        <v>53690.670005</v>
+        <v>53748.145414</v>
       </c>
       <c r="J9" t="n">
         <v>55047.565983</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1924.921181</v>
+        <v>1924.364279</v>
       </c>
       <c r="F10" t="n">
-        <v>4199.569805</v>
+        <v>4196.499577</v>
       </c>
       <c r="G10" t="n">
-        <v>6951.29511</v>
+        <v>6941.179135</v>
       </c>
       <c r="H10" t="n">
-        <v>10823.738583</v>
+        <v>10792.274199</v>
       </c>
       <c r="I10" t="n">
-        <v>16167.891058</v>
+        <v>16051.102067</v>
       </c>
       <c r="J10" t="n">
         <v>64860.59553</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47685.852885</v>
+        <v>47684.007501</v>
       </c>
       <c r="F11" t="n">
-        <v>110548.373612</v>
+        <v>110536.980657</v>
       </c>
       <c r="G11" t="n">
-        <v>203742.536904</v>
+        <v>203697.296287</v>
       </c>
       <c r="H11" t="n">
-        <v>345852.717194</v>
+        <v>345690.029866</v>
       </c>
       <c r="I11" t="n">
-        <v>546437.3978489999</v>
+        <v>545770.340414</v>
       </c>
       <c r="J11" t="n">
         <v>1086861.473158</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4225.008008</v>
+        <v>4225.394513</v>
       </c>
       <c r="F12" t="n">
-        <v>10163.938497</v>
+        <v>10166.319438</v>
       </c>
       <c r="G12" t="n">
-        <v>19752.207855</v>
+        <v>19761.641922</v>
       </c>
       <c r="H12" t="n">
-        <v>34786.249759</v>
+        <v>34820.404868</v>
       </c>
       <c r="I12" t="n">
-        <v>56048.556913</v>
+        <v>56190.355001</v>
       </c>
       <c r="J12" t="n">
         <v>37052.81582</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13068.15593</v>
+        <v>13066.966658</v>
       </c>
       <c r="F13" t="n">
-        <v>30403.743181</v>
+        <v>30396.688684</v>
       </c>
       <c r="G13" t="n">
-        <v>54643.336424</v>
+        <v>54617.926546</v>
       </c>
       <c r="H13" t="n">
-        <v>91281.466955</v>
+        <v>91196.768052</v>
       </c>
       <c r="I13" t="n">
-        <v>145263.742492</v>
+        <v>144927.300015</v>
       </c>
       <c r="J13" t="n">
         <v>357427.899519</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>246590.257521</v>
+        <v>246584.997581</v>
       </c>
       <c r="F14" t="n">
-        <v>312711.802199</v>
+        <v>312694.156711</v>
       </c>
       <c r="G14" t="n">
-        <v>424061.226636</v>
+        <v>424012.904724</v>
       </c>
       <c r="H14" t="n">
-        <v>558198.468389</v>
+        <v>558073.248971</v>
       </c>
       <c r="I14" t="n">
-        <v>711784.518957</v>
+        <v>711403.556126</v>
       </c>
       <c r="J14" t="n">
         <v>941175.323298</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>667082.955338</v>
+        <v>667097.2942220001</v>
       </c>
       <c r="F15" t="n">
-        <v>924548.6831509999</v>
+        <v>924597.750098</v>
       </c>
       <c r="G15" t="n">
-        <v>1299810.173237</v>
+        <v>1299945.083492</v>
       </c>
       <c r="H15" t="n">
-        <v>1731741.603638</v>
+        <v>1732088.617456</v>
       </c>
       <c r="I15" t="n">
-        <v>2206581.344744</v>
+        <v>2207625.598144</v>
       </c>
       <c r="J15" t="n">
         <v>2271600.581546</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>134422.477688</v>
+        <v>134423.527613</v>
       </c>
       <c r="F16" t="n">
-        <v>147675.402406</v>
+        <v>147676.634914</v>
       </c>
       <c r="G16" t="n">
-        <v>167737.565141</v>
+        <v>167736.876275</v>
       </c>
       <c r="H16" t="n">
-        <v>192234.544825</v>
+        <v>192227.204437</v>
       </c>
       <c r="I16" t="n">
-        <v>222976.877948</v>
+        <v>222945.524531</v>
       </c>
       <c r="J16" t="n">
         <v>256490.66519</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>110493.247934</v>
+        <v>110486.550628</v>
       </c>
       <c r="F17" t="n">
-        <v>141429.613719</v>
+        <v>141408.222839</v>
       </c>
       <c r="G17" t="n">
-        <v>187137.862775</v>
+        <v>187081.616974</v>
       </c>
       <c r="H17" t="n">
-        <v>237174.248526</v>
+        <v>237033.814422</v>
       </c>
       <c r="I17" t="n">
-        <v>291141.154381</v>
+        <v>290728.236943</v>
       </c>
       <c r="J17" t="n">
         <v>440960.202179</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>70519.101455</v>
+        <v>70515.669891</v>
       </c>
       <c r="F18" t="n">
-        <v>94387.12353500001</v>
+        <v>94375.86044800001</v>
       </c>
       <c r="G18" t="n">
-        <v>123634.575851</v>
+        <v>123604.922175</v>
       </c>
       <c r="H18" t="n">
-        <v>154846.002161</v>
+        <v>154771.982255</v>
       </c>
       <c r="I18" t="n">
-        <v>190617.95641</v>
+        <v>190398.936697</v>
       </c>
       <c r="J18" t="n">
         <v>282623.958227</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>36553.476751</v>
+        <v>36549.7567</v>
       </c>
       <c r="F19" t="n">
-        <v>61686.374916</v>
+        <v>61670.314869</v>
       </c>
       <c r="G19" t="n">
-        <v>86405.916685</v>
+        <v>86359.659218</v>
       </c>
       <c r="H19" t="n">
-        <v>121795.164831</v>
+        <v>121660.77389</v>
       </c>
       <c r="I19" t="n">
-        <v>169243.875119</v>
+        <v>168765.110874</v>
       </c>
       <c r="J19" t="n">
         <v>613878.720861</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10653.211988</v>
+        <v>10652.530217</v>
       </c>
       <c r="F20" t="n">
-        <v>17200.910573</v>
+        <v>17198.054027</v>
       </c>
       <c r="G20" t="n">
-        <v>24511.183083</v>
+        <v>24502.474392</v>
       </c>
       <c r="H20" t="n">
-        <v>34730.512049</v>
+        <v>34704.213966</v>
       </c>
       <c r="I20" t="n">
-        <v>47585.113917</v>
+        <v>47490.451125</v>
       </c>
       <c r="J20" t="n">
         <v>135231.138818</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>962.033903</v>
+        <v>961.962757</v>
       </c>
       <c r="F21" t="n">
-        <v>1314.464381</v>
+        <v>1314.225392</v>
       </c>
       <c r="G21" t="n">
-        <v>1589.872763</v>
+        <v>1589.287565</v>
       </c>
       <c r="H21" t="n">
-        <v>2060.392722</v>
+        <v>2058.820547</v>
       </c>
       <c r="I21" t="n">
-        <v>2737.904412</v>
+        <v>2732.447812</v>
       </c>
       <c r="J21" t="n">
         <v>7894.117349</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>69630.748954</v>
+        <v>69633.955074</v>
       </c>
       <c r="F22" t="n">
-        <v>118687.055748</v>
+        <v>118701.069843</v>
       </c>
       <c r="G22" t="n">
-        <v>167359.051763</v>
+        <v>167398.514225</v>
       </c>
       <c r="H22" t="n">
-        <v>235041.715463</v>
+        <v>235151.257383</v>
       </c>
       <c r="I22" t="n">
-        <v>322920.083026</v>
+        <v>323289.738359</v>
       </c>
       <c r="J22" t="n">
         <v>111724.049446</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7323.783633</v>
+        <v>7323.723649</v>
       </c>
       <c r="F23" t="n">
-        <v>13146.570619</v>
+        <v>13146.276495</v>
       </c>
       <c r="G23" t="n">
-        <v>20007.789989</v>
+        <v>20006.69115</v>
       </c>
       <c r="H23" t="n">
-        <v>30982.714599</v>
+        <v>30978.492604</v>
       </c>
       <c r="I23" t="n">
-        <v>47153.605578</v>
+        <v>47134.221579</v>
       </c>
       <c r="J23" t="n">
         <v>84746.889811</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5830.665816</v>
+        <v>5830.29622</v>
       </c>
       <c r="F24" t="n">
-        <v>9273.76943</v>
+        <v>9272.260654</v>
       </c>
       <c r="G24" t="n">
-        <v>12760.993143</v>
+        <v>12756.628328</v>
       </c>
       <c r="H24" t="n">
-        <v>17646.478679</v>
+        <v>17633.764326</v>
       </c>
       <c r="I24" t="n">
-        <v>23858.441963</v>
+        <v>23813.538615</v>
       </c>
       <c r="J24" t="n">
         <v>65999.960998</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1429.649329</v>
+        <v>1429.499078</v>
       </c>
       <c r="F25" t="n">
-        <v>2099.766441</v>
+        <v>2099.210122</v>
       </c>
       <c r="G25" t="n">
-        <v>2728.158107</v>
+        <v>2726.668668</v>
       </c>
       <c r="H25" t="n">
-        <v>3731.529145</v>
+        <v>3727.276075</v>
       </c>
       <c r="I25" t="n">
-        <v>5124.088313</v>
+        <v>5108.88348</v>
       </c>
       <c r="J25" t="n">
         <v>19057.928254</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>24594.612482</v>
+        <v>24592.904871</v>
       </c>
       <c r="F26" t="n">
-        <v>39761.919929</v>
+        <v>39754.944027</v>
       </c>
       <c r="G26" t="n">
-        <v>52360.656112</v>
+        <v>52342.038018</v>
       </c>
       <c r="H26" t="n">
-        <v>69729.143024</v>
+        <v>69678.627276</v>
       </c>
       <c r="I26" t="n">
-        <v>92163.432612</v>
+        <v>91993.576506</v>
       </c>
       <c r="J26" t="n">
         <v>246973.758559</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>50786.931115</v>
+        <v>50788.309653</v>
       </c>
       <c r="F27" t="n">
-        <v>85238.913734</v>
+        <v>85244.86917000001</v>
       </c>
       <c r="G27" t="n">
-        <v>116109.009664</v>
+        <v>116125.117334</v>
       </c>
       <c r="H27" t="n">
-        <v>161138.278638</v>
+        <v>161181.764189</v>
       </c>
       <c r="I27" t="n">
-        <v>223502.872621</v>
+        <v>223647.325712</v>
       </c>
       <c r="J27" t="n">
         <v>172229.429323</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>36516.330329</v>
+        <v>36518.50608</v>
       </c>
       <c r="F28" t="n">
-        <v>55640.225471</v>
+        <v>55648.746641</v>
       </c>
       <c r="G28" t="n">
-        <v>83006.689636</v>
+        <v>83032.242046</v>
       </c>
       <c r="H28" t="n">
-        <v>131940.185025</v>
+        <v>132021.123919</v>
       </c>
       <c r="I28" t="n">
-        <v>206458.819513</v>
+        <v>206772.943013</v>
       </c>
       <c r="J28" t="n">
         <v>8008.049055</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1001.190004</v>
+        <v>1001.143742</v>
       </c>
       <c r="F29" t="n">
-        <v>1454.721433</v>
+        <v>1454.55192</v>
       </c>
       <c r="G29" t="n">
-        <v>2162.714173</v>
+        <v>2162.189198</v>
       </c>
       <c r="H29" t="n">
-        <v>3348.414664</v>
+        <v>3346.71256</v>
       </c>
       <c r="I29" t="n">
-        <v>5012.238332</v>
+        <v>5005.599332</v>
       </c>
       <c r="J29" t="n">
         <v>23927.436948</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5739.297918</v>
+        <v>5739.323555</v>
       </c>
       <c r="F30" t="n">
-        <v>7784.288617</v>
+        <v>7784.39511</v>
       </c>
       <c r="G30" t="n">
-        <v>10881.705254</v>
+        <v>10882.012435</v>
       </c>
       <c r="H30" t="n">
-        <v>16451.653248</v>
+        <v>16452.571897</v>
       </c>
       <c r="I30" t="n">
-        <v>24053.351195</v>
+        <v>24056.792943</v>
       </c>
       <c r="J30" t="n">
         <v>23228.679066</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1644.318865</v>
+        <v>1644.333118</v>
       </c>
       <c r="F31" t="n">
-        <v>2446.462171</v>
+        <v>2446.518392</v>
       </c>
       <c r="G31" t="n">
-        <v>3549.454063</v>
+        <v>3549.615777</v>
       </c>
       <c r="H31" t="n">
-        <v>5393.391833</v>
+        <v>5393.875016</v>
       </c>
       <c r="I31" t="n">
-        <v>7932.487197</v>
+        <v>7934.273271</v>
       </c>
       <c r="J31" t="n">
         <v>6071.346033</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>26423.813384</v>
+        <v>26424.140902</v>
       </c>
       <c r="F32" t="n">
-        <v>35179.26427</v>
+        <v>35180.433637</v>
       </c>
       <c r="G32" t="n">
-        <v>48034.138884</v>
+        <v>48037.376154</v>
       </c>
       <c r="H32" t="n">
-        <v>71039.903707</v>
+        <v>71049.52806500001</v>
       </c>
       <c r="I32" t="n">
-        <v>105023.188005</v>
+        <v>105059.333447</v>
       </c>
       <c r="J32" t="n">
         <v>50061.368486</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>24191.606851</v>
+        <v>24191.783126</v>
       </c>
       <c r="F33" t="n">
-        <v>35045.702662</v>
+        <v>35046.391374</v>
       </c>
       <c r="G33" t="n">
-        <v>51757.16331</v>
+        <v>51759.14199</v>
       </c>
       <c r="H33" t="n">
-        <v>80008.009953</v>
+        <v>80013.889303</v>
       </c>
       <c r="I33" t="n">
-        <v>119520.492185</v>
+        <v>119542.169665</v>
       </c>
       <c r="J33" t="n">
         <v>106025.298874</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27163.827254</v>
+        <v>27164.208683</v>
       </c>
       <c r="F34" t="n">
-        <v>69088.264091</v>
+        <v>69090.667159</v>
       </c>
       <c r="G34" t="n">
-        <v>172939.818814</v>
+        <v>172950.980842</v>
       </c>
       <c r="H34" t="n">
-        <v>386434.650164</v>
+        <v>386481.006961</v>
       </c>
       <c r="I34" t="n">
-        <v>729769.530183</v>
+        <v>729979.6578639999</v>
       </c>
       <c r="J34" t="n">
         <v>531654.822376</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8399.552264</v>
+        <v>8399.618997</v>
       </c>
       <c r="F35" t="n">
-        <v>15027.698185</v>
+        <v>15027.99127</v>
       </c>
       <c r="G35" t="n">
-        <v>26727.959115</v>
+        <v>26728.876981</v>
       </c>
       <c r="H35" t="n">
-        <v>45792.529457</v>
+        <v>45795.338122</v>
       </c>
       <c r="I35" t="n">
-        <v>70798.601687</v>
+        <v>70809.026547</v>
       </c>
       <c r="J35" t="n">
         <v>68026.441949</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>176.068663</v>
+        <v>176.049406</v>
       </c>
       <c r="F36" t="n">
-        <v>253.645106</v>
+        <v>253.572301</v>
       </c>
       <c r="G36" t="n">
-        <v>330.878628</v>
+        <v>330.685116</v>
       </c>
       <c r="H36" t="n">
-        <v>439.615536</v>
+        <v>439.095894</v>
       </c>
       <c r="I36" t="n">
-        <v>571.096781</v>
+        <v>569.39552</v>
       </c>
       <c r="J36" t="n">
         <v>4493.238132</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7326.049859</v>
+        <v>7325.996251</v>
       </c>
       <c r="F37" t="n">
-        <v>9433.362965</v>
+        <v>9433.214134</v>
       </c>
       <c r="G37" t="n">
-        <v>12318.205967</v>
+        <v>12317.825987</v>
       </c>
       <c r="H37" t="n">
-        <v>17190.758893</v>
+        <v>17189.668222</v>
       </c>
       <c r="I37" t="n">
-        <v>23680.324421</v>
+        <v>23676.47745</v>
       </c>
       <c r="J37" t="n">
         <v>38757.974328</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>35065.96181</v>
+        <v>35066.384359</v>
       </c>
       <c r="F38" t="n">
-        <v>51622.178345</v>
+        <v>51623.82733</v>
       </c>
       <c r="G38" t="n">
-        <v>73895.68021599999</v>
+        <v>73900.44644299999</v>
       </c>
       <c r="H38" t="n">
-        <v>111490.066497</v>
+        <v>111504.516094</v>
       </c>
       <c r="I38" t="n">
-        <v>165335.09201</v>
+        <v>165389.677102</v>
       </c>
       <c r="J38" t="n">
         <v>83917.22532300001</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3718.910662</v>
+        <v>3718.93378</v>
       </c>
       <c r="F39" t="n">
-        <v>5259.182144</v>
+        <v>5259.271732</v>
       </c>
       <c r="G39" t="n">
-        <v>7847.629929</v>
+        <v>7847.883762</v>
       </c>
       <c r="H39" t="n">
-        <v>12413.781585</v>
+        <v>12414.520715</v>
       </c>
       <c r="I39" t="n">
-        <v>18891.37665</v>
+        <v>18894.03878</v>
       </c>
       <c r="J39" t="n">
         <v>19251.035247</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>568.063249</v>
+        <v>568.064578</v>
       </c>
       <c r="F40" t="n">
-        <v>831.673093</v>
+        <v>831.678643</v>
       </c>
       <c r="G40" t="n">
-        <v>1215.797209</v>
+        <v>1215.810961</v>
       </c>
       <c r="H40" t="n">
-        <v>1828.838001</v>
+        <v>1828.871575</v>
       </c>
       <c r="I40" t="n">
-        <v>2682.172891</v>
+        <v>2682.277378</v>
       </c>
       <c r="J40" t="n">
         <v>3307.912014</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>668.523139</v>
+        <v>668.510121</v>
       </c>
       <c r="F41" t="n">
-        <v>1081.069218</v>
+        <v>1081.012518</v>
       </c>
       <c r="G41" t="n">
-        <v>1631.4872</v>
+        <v>1631.303285</v>
       </c>
       <c r="H41" t="n">
-        <v>2505.870371</v>
+        <v>2505.26817</v>
       </c>
       <c r="I41" t="n">
-        <v>3690.817439</v>
+        <v>3688.487703</v>
       </c>
       <c r="J41" t="n">
         <v>10813.747445</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3941.146653</v>
+        <v>3940.93108</v>
       </c>
       <c r="F42" t="n">
-        <v>5423.193898</v>
+        <v>5422.460737</v>
       </c>
       <c r="G42" t="n">
-        <v>7452.742419</v>
+        <v>7450.711825</v>
       </c>
       <c r="H42" t="n">
-        <v>10694.214626</v>
+        <v>10688.304288</v>
       </c>
       <c r="I42" t="n">
-        <v>14920.555903</v>
+        <v>14899.696189</v>
       </c>
       <c r="J42" t="n">
         <v>68172.461784</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1657.526983</v>
+        <v>1657.548422</v>
       </c>
       <c r="F43" t="n">
-        <v>3267.670279</v>
+        <v>3267.778296</v>
       </c>
       <c r="G43" t="n">
-        <v>6108.888311</v>
+        <v>6109.281452</v>
       </c>
       <c r="H43" t="n">
-        <v>11146.984787</v>
+        <v>11148.385134</v>
       </c>
       <c r="I43" t="n">
-        <v>19283.156546</v>
+        <v>19289.167363</v>
       </c>
       <c r="J43" t="n">
         <v>12430.296329</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7732.293992</v>
+        <v>7732.323185</v>
       </c>
       <c r="F44" t="n">
-        <v>12261.183406</v>
+        <v>12261.306209</v>
       </c>
       <c r="G44" t="n">
-        <v>20006.422289</v>
+        <v>20006.75573</v>
       </c>
       <c r="H44" t="n">
-        <v>34213.79764</v>
+        <v>34214.649186</v>
       </c>
       <c r="I44" t="n">
-        <v>55733.533813</v>
+        <v>55736.117064</v>
       </c>
       <c r="J44" t="n">
         <v>74198.353495</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4607.763447</v>
+        <v>4607.802859</v>
       </c>
       <c r="F45" t="n">
-        <v>7090.845563</v>
+        <v>7091.004942</v>
       </c>
       <c r="G45" t="n">
-        <v>10635.184623</v>
+        <v>10635.652943</v>
       </c>
       <c r="H45" t="n">
-        <v>16389.233497</v>
+        <v>16390.645516</v>
       </c>
       <c r="I45" t="n">
-        <v>24293.909571</v>
+        <v>24299.163899</v>
       </c>
       <c r="J45" t="n">
         <v>19231.347739</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1610.83551</v>
+        <v>1610.818771</v>
       </c>
       <c r="F46" t="n">
-        <v>2629.785388</v>
+        <v>2629.714308</v>
       </c>
       <c r="G46" t="n">
-        <v>4410.801775</v>
+        <v>4410.52973</v>
       </c>
       <c r="H46" t="n">
-        <v>7681.626034</v>
+        <v>7680.550153</v>
       </c>
       <c r="I46" t="n">
-        <v>12703.249944</v>
+        <v>12698.381994</v>
       </c>
       <c r="J46" t="n">
         <v>32965.40969</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>136562.265135</v>
+        <v>136561.113731</v>
       </c>
       <c r="F47" t="n">
-        <v>232654.191411</v>
+        <v>232648.587622</v>
       </c>
       <c r="G47" t="n">
-        <v>370768.122871</v>
+        <v>370747.697886</v>
       </c>
       <c r="H47" t="n">
-        <v>601925.957381</v>
+        <v>601851.948071</v>
       </c>
       <c r="I47" t="n">
-        <v>941245.638314</v>
+        <v>940931.465583</v>
       </c>
       <c r="J47" t="n">
         <v>2213699.48541</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12591.765704</v>
+        <v>12591.858669</v>
       </c>
       <c r="F48" t="n">
-        <v>18586.257341</v>
+        <v>18586.62751</v>
       </c>
       <c r="G48" t="n">
-        <v>27363.226147</v>
+        <v>27364.300717</v>
       </c>
       <c r="H48" t="n">
-        <v>41475.796341</v>
+        <v>41479.001339</v>
       </c>
       <c r="I48" t="n">
-        <v>60411.730526</v>
+        <v>60423.569937</v>
       </c>
       <c r="J48" t="n">
         <v>49464.933065</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2248.327229</v>
+        <v>2248.328511</v>
       </c>
       <c r="F49" t="n">
-        <v>3516.242323</v>
+        <v>3516.247135</v>
       </c>
       <c r="G49" t="n">
-        <v>5285.981271</v>
+        <v>5285.98148</v>
       </c>
       <c r="H49" t="n">
-        <v>8077.098061</v>
+        <v>8077.059774</v>
       </c>
       <c r="I49" t="n">
-        <v>11807.886153</v>
+        <v>11807.683477</v>
       </c>
       <c r="J49" t="n">
         <v>16162.386704</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>60.045827</v>
+        <v>60.044398</v>
       </c>
       <c r="F50" t="n">
-        <v>85.71516099999999</v>
+        <v>85.70988699999999</v>
       </c>
       <c r="G50" t="n">
-        <v>114.48207</v>
+        <v>114.467597</v>
       </c>
       <c r="H50" t="n">
-        <v>156.13929</v>
+        <v>156.099073</v>
       </c>
       <c r="I50" t="n">
-        <v>206.495481</v>
+        <v>206.360943</v>
       </c>
       <c r="J50" t="n">
         <v>553.577903</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>880.011926</v>
+        <v>879.910837</v>
       </c>
       <c r="F51" t="n">
-        <v>1231.440374</v>
+        <v>1231.086392</v>
       </c>
       <c r="G51" t="n">
-        <v>1745.615108</v>
+        <v>1744.596412</v>
       </c>
       <c r="H51" t="n">
-        <v>2603.299646</v>
+        <v>2600.196414</v>
       </c>
       <c r="I51" t="n">
-        <v>3816.609621</v>
+        <v>3804.976081</v>
       </c>
       <c r="J51" t="n">
         <v>34546.286805</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>910.06267</v>
+        <v>910.057921</v>
       </c>
       <c r="F52" t="n">
-        <v>1142.748951</v>
+        <v>1142.73783</v>
       </c>
       <c r="G52" t="n">
-        <v>1459.604767</v>
+        <v>1459.579707</v>
       </c>
       <c r="H52" t="n">
-        <v>2041.770098</v>
+        <v>2041.699767</v>
       </c>
       <c r="I52" t="n">
-        <v>2869.903462</v>
+        <v>2869.648778</v>
       </c>
       <c r="J52" t="n">
         <v>4503.573164</v>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>872951.844986</v>
+        <v>872951.764361</v>
       </c>
       <c r="F54" t="n">
-        <v>939791.964457</v>
+        <v>939791.762465</v>
       </c>
       <c r="G54" t="n">
-        <v>1087327.790376</v>
+        <v>1087327.34866</v>
       </c>
       <c r="H54" t="n">
-        <v>1287042.575246</v>
+        <v>1287041.573966</v>
       </c>
       <c r="I54" t="n">
-        <v>1506215.44846</v>
+        <v>1506212.629388</v>
       </c>
       <c r="J54" t="n">
         <v>1783408.362293</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>155035.180614</v>
+        <v>155035.261239</v>
       </c>
       <c r="F55" t="n">
-        <v>155472.597903</v>
+        <v>155472.799895</v>
       </c>
       <c r="G55" t="n">
-        <v>170359.666424</v>
+        <v>170360.10814</v>
       </c>
       <c r="H55" t="n">
-        <v>193754.746454</v>
+        <v>193755.747734</v>
       </c>
       <c r="I55" t="n">
-        <v>220108.47694</v>
+        <v>220111.296012</v>
       </c>
       <c r="J55" t="n">
         <v>183022.201107</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>19769.207531</v>
+        <v>19770.370372</v>
       </c>
       <c r="F58" t="n">
-        <v>26024.650348</v>
+        <v>26028.593914</v>
       </c>
       <c r="G58" t="n">
-        <v>35698.219828</v>
+        <v>35709.212826</v>
       </c>
       <c r="H58" t="n">
-        <v>47193.927215</v>
+        <v>47223.29119</v>
       </c>
       <c r="I58" t="n">
-        <v>60469.895475</v>
+        <v>60564.289377</v>
       </c>
       <c r="J58" t="n">
         <v>28148.069771</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>18361.627015</v>
+        <v>18363.204208</v>
       </c>
       <c r="F59" t="n">
-        <v>25060.626268</v>
+        <v>25066.128742</v>
       </c>
       <c r="G59" t="n">
-        <v>35501.133264</v>
+        <v>35516.928667</v>
       </c>
       <c r="H59" t="n">
-        <v>47225.891927</v>
+        <v>47268.314956</v>
       </c>
       <c r="I59" t="n">
-        <v>60330.996541</v>
+        <v>60467.087569</v>
       </c>
       <c r="J59" t="n">
         <v>7723.533267</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>14917.1124</v>
+        <v>14918.162813</v>
       </c>
       <c r="F60" t="n">
-        <v>15908.555103</v>
+        <v>15911.44465</v>
       </c>
       <c r="G60" t="n">
-        <v>17943.339899</v>
+        <v>17949.985113</v>
       </c>
       <c r="H60" t="n">
-        <v>20693.783194</v>
+        <v>20709.305874</v>
       </c>
       <c r="I60" t="n">
-        <v>24368.699056</v>
+        <v>24414.634139</v>
       </c>
       <c r="J60" t="n">
         <v>7182.699157</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38923.78322</v>
+        <v>38923.650312</v>
       </c>
       <c r="F61" t="n">
-        <v>51704.414025</v>
+        <v>51704.158336</v>
       </c>
       <c r="G61" t="n">
-        <v>68712.558531</v>
+        <v>68712.18743200001</v>
       </c>
       <c r="H61" t="n">
-        <v>87790.133915</v>
+        <v>87789.72953</v>
       </c>
       <c r="I61" t="n">
-        <v>110102.058865</v>
+        <v>110102.046941</v>
       </c>
       <c r="J61" t="n">
         <v>133039.405308</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>73049.995417</v>
+        <v>73046.988344</v>
       </c>
       <c r="F62" t="n">
-        <v>101348.074628</v>
+        <v>101337.593543</v>
       </c>
       <c r="G62" t="n">
-        <v>136681.231549</v>
+        <v>136652.782282</v>
       </c>
       <c r="H62" t="n">
-        <v>172002.497291</v>
+        <v>171930.784112</v>
       </c>
       <c r="I62" t="n">
-        <v>207810.963927</v>
+        <v>207596.736459</v>
       </c>
       <c r="J62" t="n">
         <v>333673.550291</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>64791.919251</v>
+        <v>64790.479171</v>
       </c>
       <c r="F63" t="n">
-        <v>88775.11928</v>
+        <v>88770.38024</v>
       </c>
       <c r="G63" t="n">
-        <v>117645.128975</v>
+        <v>117633.01403</v>
       </c>
       <c r="H63" t="n">
-        <v>149383.077759</v>
+        <v>149353.152109</v>
       </c>
       <c r="I63" t="n">
-        <v>189672.010348</v>
+        <v>189578.791126</v>
       </c>
       <c r="J63" t="n">
         <v>280124.858018</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5786.448051</v>
+        <v>5786.924301</v>
       </c>
       <c r="F64" t="n">
-        <v>6976.164294</v>
+        <v>6977.634538</v>
       </c>
       <c r="G64" t="n">
-        <v>9011.88607</v>
+        <v>9015.738211</v>
       </c>
       <c r="H64" t="n">
-        <v>11475.517497</v>
+        <v>11485.422851</v>
       </c>
       <c r="I64" t="n">
-        <v>14395.699251</v>
+        <v>14426.894435</v>
       </c>
       <c r="J64" t="n">
         <v>2433.854495</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>42101.845019</v>
+        <v>42099.310037</v>
       </c>
       <c r="F65" t="n">
-        <v>60157.082731</v>
+        <v>60148.106728</v>
       </c>
       <c r="G65" t="n">
-        <v>86676.81816</v>
+        <v>86650.951823</v>
       </c>
       <c r="H65" t="n">
-        <v>119205.353979</v>
+        <v>119134.132415</v>
       </c>
       <c r="I65" t="n">
-        <v>160040.55165</v>
+        <v>159803.279955</v>
       </c>
       <c r="J65" t="n">
         <v>324689.944924</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>32563.849158</v>
+        <v>32565.068549</v>
       </c>
       <c r="F66" t="n">
-        <v>45876.871337</v>
+        <v>45881.327207</v>
       </c>
       <c r="G66" t="n">
-        <v>65373.20114</v>
+        <v>65386.126801</v>
       </c>
       <c r="H66" t="n">
-        <v>88849.485909</v>
+        <v>88884.967376</v>
       </c>
       <c r="I66" t="n">
-        <v>117429.735926</v>
+        <v>117547.093525</v>
       </c>
       <c r="J66" t="n">
         <v>89864.220885</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3742.625832</v>
+        <v>3742.118592</v>
       </c>
       <c r="F67" t="n">
-        <v>5417.268201</v>
+        <v>5415.41565</v>
       </c>
       <c r="G67" t="n">
-        <v>8224.497791</v>
+        <v>8218.774098</v>
       </c>
       <c r="H67" t="n">
-        <v>11996.640442</v>
+        <v>11979.676132</v>
       </c>
       <c r="I67" t="n">
-        <v>17019.489027</v>
+        <v>16959.26615</v>
       </c>
       <c r="J67" t="n">
         <v>54861.250837</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>14840.270387</v>
+        <v>14840.026459</v>
       </c>
       <c r="F68" t="n">
-        <v>21231.440055</v>
+        <v>21230.574316</v>
       </c>
       <c r="G68" t="n">
-        <v>32223.466522</v>
+        <v>32220.679045</v>
       </c>
       <c r="H68" t="n">
-        <v>45653.880075</v>
+        <v>45645.544661</v>
       </c>
       <c r="I68" t="n">
-        <v>60471.354805</v>
+        <v>60443.092795</v>
       </c>
       <c r="J68" t="n">
         <v>87299.92845599999</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>9869.381955999999</v>
+        <v>9870.167324</v>
       </c>
       <c r="F69" t="n">
-        <v>12817.014143</v>
+        <v>12819.625119</v>
       </c>
       <c r="G69" t="n">
-        <v>16948.812648</v>
+        <v>16955.816645</v>
       </c>
       <c r="H69" t="n">
-        <v>21523.893744</v>
+        <v>21541.862042</v>
       </c>
       <c r="I69" t="n">
-        <v>26714.616723</v>
+        <v>26770.618534</v>
       </c>
       <c r="J69" t="n">
         <v>5426.713419</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>16488.064036</v>
+        <v>16488.869839</v>
       </c>
       <c r="F70" t="n">
-        <v>22327.98412</v>
+        <v>22330.798658</v>
       </c>
       <c r="G70" t="n">
-        <v>31178.606287</v>
+        <v>31186.583451</v>
       </c>
       <c r="H70" t="n">
-        <v>42017.776906</v>
+        <v>42039.442877</v>
       </c>
       <c r="I70" t="n">
-        <v>55508.043532</v>
+        <v>55579.548022</v>
       </c>
       <c r="J70" t="n">
         <v>34656.973311</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>37059.656404</v>
+        <v>37060.190481</v>
       </c>
       <c r="F71" t="n">
-        <v>54161.995095</v>
+        <v>54164.057112</v>
       </c>
       <c r="G71" t="n">
-        <v>74474.792888</v>
+        <v>74480.723086</v>
       </c>
       <c r="H71" t="n">
-        <v>95532.951049</v>
+        <v>95548.76009900001</v>
       </c>
       <c r="I71" t="n">
-        <v>118327.02156</v>
+        <v>118377.342356</v>
       </c>
       <c r="J71" t="n">
         <v>118158.586852</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21814.191687</v>
+        <v>21813.783383</v>
       </c>
       <c r="F72" t="n">
-        <v>27224.799095</v>
+        <v>27223.626216</v>
       </c>
       <c r="G72" t="n">
-        <v>35236.961234</v>
+        <v>35234.031761</v>
       </c>
       <c r="H72" t="n">
-        <v>44661.853531</v>
+        <v>44654.498731</v>
       </c>
       <c r="I72" t="n">
-        <v>56331.025975</v>
+        <v>56307.861708</v>
       </c>
       <c r="J72" t="n">
         <v>79925.58794700001</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>34451.292009</v>
+        <v>34451.453351</v>
       </c>
       <c r="F73" t="n">
-        <v>34913.735922</v>
+        <v>34914.428871</v>
       </c>
       <c r="G73" t="n">
-        <v>33285.933864</v>
+        <v>33287.780618</v>
       </c>
       <c r="H73" t="n">
-        <v>33586.126937</v>
+        <v>33590.545215</v>
       </c>
       <c r="I73" t="n">
-        <v>36625.833704</v>
+        <v>36638.834275</v>
       </c>
       <c r="J73" t="n">
         <v>35085.63401</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5929.820627</v>
+        <v>5930.322463</v>
       </c>
       <c r="F74" t="n">
-        <v>8801.152458</v>
+        <v>8803.053260000001</v>
       </c>
       <c r="G74" t="n">
-        <v>12050.67685</v>
+        <v>12055.94961</v>
       </c>
       <c r="H74" t="n">
-        <v>15122.574129</v>
+        <v>15135.935329</v>
       </c>
       <c r="I74" t="n">
-        <v>18288.515133</v>
+        <v>18329.094135</v>
       </c>
       <c r="J74" t="n">
         <v>2562.716554</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>29628.923394</v>
+        <v>29628.738592</v>
       </c>
       <c r="F75" t="n">
-        <v>36914.997655</v>
+        <v>36914.269621</v>
       </c>
       <c r="G75" t="n">
-        <v>43660.658105</v>
+        <v>43658.219206</v>
       </c>
       <c r="H75" t="n">
-        <v>50490.705154</v>
+        <v>50483.87251</v>
       </c>
       <c r="I75" t="n">
-        <v>57039.640558</v>
+        <v>57018.823201</v>
       </c>
       <c r="J75" t="n">
         <v>85364.12147899999</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>93903.991047</v>
+        <v>93896.143696</v>
       </c>
       <c r="F76" t="n">
-        <v>121187.552529</v>
+        <v>121162.297025</v>
       </c>
       <c r="G76" t="n">
-        <v>117731.999318</v>
+        <v>117681.111219</v>
       </c>
       <c r="H76" t="n">
-        <v>116655.308677</v>
+        <v>116552.382603</v>
       </c>
       <c r="I76" t="n">
-        <v>123843.053671</v>
+        <v>123575.625256</v>
       </c>
       <c r="J76" t="n">
         <v>406733.967813</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>41155.82691</v>
+        <v>41155.535763</v>
       </c>
       <c r="F77" t="n">
-        <v>58298.564283</v>
+        <v>58297.365738</v>
       </c>
       <c r="G77" t="n">
-        <v>72356.15142900001</v>
+        <v>72352.066922</v>
       </c>
       <c r="H77" t="n">
-        <v>81019.10376500001</v>
+        <v>81008.00941</v>
       </c>
       <c r="I77" t="n">
-        <v>84270.287707</v>
+        <v>84238.778234</v>
       </c>
       <c r="J77" t="n">
         <v>116629.618142</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>349028.296251</v>
+        <v>349028.591533</v>
       </c>
       <c r="F78" t="n">
-        <v>377918.71544</v>
+        <v>377917.24727</v>
       </c>
       <c r="G78" t="n">
-        <v>379487.437363</v>
+        <v>379476.794368</v>
       </c>
       <c r="H78" t="n">
-        <v>397549.51055</v>
+        <v>397515.708173</v>
       </c>
       <c r="I78" t="n">
-        <v>433158.854195</v>
+        <v>433050.984537</v>
       </c>
       <c r="J78" t="n">
         <v>604553.607844</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>49477.591483</v>
+        <v>49478.84651</v>
       </c>
       <c r="F79" t="n">
-        <v>81032.312991</v>
+        <v>81037.04023699999</v>
       </c>
       <c r="G79" t="n">
-        <v>126185.531898</v>
+        <v>126197.989991</v>
       </c>
       <c r="H79" t="n">
-        <v>180860.932639</v>
+        <v>180891.85694</v>
       </c>
       <c r="I79" t="n">
-        <v>236318.108529</v>
+        <v>236409.044737</v>
       </c>
       <c r="J79" t="n">
         <v>194747.396428</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>20937.082491</v>
+        <v>20937.41444</v>
       </c>
       <c r="F80" t="n">
-        <v>22461.830422</v>
+        <v>22462.570905</v>
       </c>
       <c r="G80" t="n">
-        <v>23313.423381</v>
+        <v>23314.474282</v>
       </c>
       <c r="H80" t="n">
-        <v>25947.390857</v>
+        <v>25948.966996</v>
       </c>
       <c r="I80" t="n">
-        <v>30161.411312</v>
+        <v>30164.729656</v>
       </c>
       <c r="J80" t="n">
         <v>33193.461648</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>65163.82859</v>
+        <v>65165.727749</v>
       </c>
       <c r="F81" t="n">
-        <v>109736.030911</v>
+        <v>109743.444796</v>
       </c>
       <c r="G81" t="n">
-        <v>171885.879523</v>
+        <v>171905.925248</v>
       </c>
       <c r="H81" t="n">
-        <v>246631.298989</v>
+        <v>246682.095066</v>
       </c>
       <c r="I81" t="n">
-        <v>322710.917569</v>
+        <v>322862.725524</v>
       </c>
       <c r="J81" t="n">
         <v>235965.551747</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>85583.084967</v>
+        <v>85584.168899</v>
       </c>
       <c r="F82" t="n">
-        <v>107716.098581</v>
+        <v>107718.909858</v>
       </c>
       <c r="G82" t="n">
-        <v>124666.033129</v>
+        <v>124670.126265</v>
       </c>
       <c r="H82" t="n">
-        <v>146063.341194</v>
+        <v>146068.865982</v>
       </c>
       <c r="I82" t="n">
-        <v>170764.235348</v>
+        <v>170773.583314</v>
       </c>
       <c r="J82" t="n">
         <v>193467.171258</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>218037.309868</v>
+        <v>218040.767819</v>
       </c>
       <c r="F83" t="n">
-        <v>365112.652036</v>
+        <v>365125.609397</v>
       </c>
       <c r="G83" t="n">
-        <v>560057.327755</v>
+        <v>560087.7343989999</v>
       </c>
       <c r="H83" t="n">
-        <v>785215.148516</v>
+        <v>785280.98266</v>
       </c>
       <c r="I83" t="n">
-        <v>1002976.54663</v>
+        <v>1003148.761062</v>
       </c>
       <c r="J83" t="n">
         <v>1039830.217585</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>166049.049472</v>
+        <v>166050.388822</v>
       </c>
       <c r="F86" t="n">
-        <v>184433.299845</v>
+        <v>184437.047077</v>
       </c>
       <c r="G86" t="n">
-        <v>208373.476697</v>
+        <v>208381.986646</v>
       </c>
       <c r="H86" t="n">
-        <v>237224.238075</v>
+        <v>237243.579926</v>
       </c>
       <c r="I86" t="n">
-        <v>266444.803059</v>
+        <v>266498.411173</v>
       </c>
       <c r="J86" t="n">
         <v>146015.422605</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>15456.793689</v>
+        <v>15456.704465</v>
       </c>
       <c r="F87" t="n">
-        <v>19335.065883</v>
+        <v>19334.796665</v>
       </c>
       <c r="G87" t="n">
-        <v>25095.598076</v>
+        <v>25094.923596</v>
       </c>
       <c r="H87" t="n">
-        <v>32113.305483</v>
+        <v>32111.623015</v>
       </c>
       <c r="I87" t="n">
-        <v>39769.933082</v>
+        <v>39764.861882</v>
       </c>
       <c r="J87" t="n">
         <v>63563.834998</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>281524.840039</v>
+        <v>281525.957643</v>
       </c>
       <c r="F88" t="n">
-        <v>280939.217222</v>
+        <v>280942.017648</v>
       </c>
       <c r="G88" t="n">
-        <v>293249.504429</v>
+        <v>293255.364917</v>
       </c>
       <c r="H88" t="n">
-        <v>323924.853819</v>
+        <v>323937.74137</v>
       </c>
       <c r="I88" t="n">
-        <v>365301.966298</v>
+        <v>365337.676762</v>
       </c>
       <c r="J88" t="n">
         <v>314582.09425</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>34580.572596</v>
+        <v>34580.800004</v>
       </c>
       <c r="F89" t="n">
-        <v>36602.433527</v>
+        <v>36603.039522</v>
       </c>
       <c r="G89" t="n">
-        <v>41209.585873</v>
+        <v>41210.959409</v>
       </c>
       <c r="H89" t="n">
-        <v>46993.624229</v>
+        <v>46996.752904</v>
       </c>
       <c r="I89" t="n">
-        <v>52914.575461</v>
+        <v>52923.260794</v>
       </c>
       <c r="J89" t="n">
         <v>34595.976343</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103489.695782</v>
+        <v>103488.984718</v>
       </c>
       <c r="F90" t="n">
-        <v>111354.957229</v>
+        <v>111353.083653</v>
       </c>
       <c r="G90" t="n">
-        <v>128313.189844</v>
+        <v>128308.973009</v>
       </c>
       <c r="H90" t="n">
-        <v>150761.280472</v>
+        <v>150751.562007</v>
       </c>
       <c r="I90" t="n">
-        <v>174860.685217</v>
+        <v>174833.192856</v>
       </c>
       <c r="J90" t="n">
         <v>278934.309355</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>14527.906481</v>
+        <v>14527.397069</v>
       </c>
       <c r="F91" t="n">
-        <v>16151.170397</v>
+        <v>16149.773072</v>
       </c>
       <c r="G91" t="n">
-        <v>18474.702635</v>
+        <v>18471.548739</v>
       </c>
       <c r="H91" t="n">
-        <v>20994.505824</v>
+        <v>20987.444118</v>
       </c>
       <c r="I91" t="n">
-        <v>23464.355752</v>
+        <v>23445.262129</v>
       </c>
       <c r="J91" t="n">
         <v>78095.80931900001</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>18863.918185</v>
+        <v>18863.774333</v>
       </c>
       <c r="F92" t="n">
-        <v>21106.363454</v>
+        <v>21105.971534</v>
       </c>
       <c r="G92" t="n">
-        <v>24851.313422</v>
+        <v>24850.414908</v>
       </c>
       <c r="H92" t="n">
-        <v>28900.411414</v>
+        <v>28898.360775</v>
       </c>
       <c r="I92" t="n">
-        <v>32671.659499</v>
+        <v>32665.993561</v>
       </c>
       <c r="J92" t="n">
         <v>52182.98315</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4449.481573</v>
+        <v>4449.419618</v>
       </c>
       <c r="F93" t="n">
-        <v>5220.376033</v>
+        <v>5220.197692</v>
       </c>
       <c r="G93" t="n">
-        <v>6517.359253</v>
+        <v>6516.923245</v>
       </c>
       <c r="H93" t="n">
-        <v>8265.854960999999</v>
+        <v>8264.771585</v>
       </c>
       <c r="I93" t="n">
-        <v>10273.896852</v>
+        <v>10270.631496</v>
       </c>
       <c r="J93" t="n">
         <v>22295.622581</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>560122.402908</v>
+        <v>560121.235219</v>
       </c>
       <c r="F94" t="n">
-        <v>659253.24011</v>
+        <v>659250.075175</v>
       </c>
       <c r="G94" t="n">
-        <v>772569.028642</v>
+        <v>772562.086501</v>
       </c>
       <c r="H94" t="n">
-        <v>894347.018543</v>
+        <v>894331.508757</v>
       </c>
       <c r="I94" t="n">
-        <v>1008771.585305</v>
+        <v>1008728.745375</v>
       </c>
       <c r="J94" t="n">
         <v>1244623.286994</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>224664.536329</v>
+        <v>224664.597289</v>
       </c>
       <c r="F95" t="n">
-        <v>268942.104391</v>
+        <v>268942.397138</v>
       </c>
       <c r="G95" t="n">
-        <v>327408.274507</v>
+        <v>327409.212935</v>
       </c>
       <c r="H95" t="n">
-        <v>392958.917644</v>
+        <v>392961.45403</v>
       </c>
       <c r="I95" t="n">
-        <v>457718.141069</v>
+        <v>457725.734707</v>
       </c>
       <c r="J95" t="n">
         <v>498904.519848</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>90769.701283</v>
+        <v>90769.511365</v>
       </c>
       <c r="F96" t="n">
-        <v>94781.82152</v>
+        <v>94781.341825</v>
       </c>
       <c r="G96" t="n">
-        <v>99695.601335</v>
+        <v>99694.610159</v>
       </c>
       <c r="H96" t="n">
-        <v>109259.363954</v>
+        <v>109257.208739</v>
       </c>
       <c r="I96" t="n">
-        <v>121596.97946</v>
+        <v>121591.048445</v>
       </c>
       <c r="J96" t="n">
         <v>153809.665241</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>50493.201662</v>
+        <v>50493.329454</v>
       </c>
       <c r="F97" t="n">
-        <v>48693.21169</v>
+        <v>48693.520299</v>
       </c>
       <c r="G97" t="n">
-        <v>49686.117586</v>
+        <v>49686.748237</v>
       </c>
       <c r="H97" t="n">
-        <v>54200.587981</v>
+        <v>54201.955174</v>
       </c>
       <c r="I97" t="n">
-        <v>60877.354545</v>
+        <v>60881.11642</v>
       </c>
       <c r="J97" t="n">
         <v>58654.588916</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>208542.827779</v>
+        <v>208542.460607</v>
       </c>
       <c r="F98" t="n">
-        <v>203368.694155</v>
+        <v>203367.820263</v>
       </c>
       <c r="G98" t="n">
-        <v>206428.541662</v>
+        <v>206426.781888</v>
       </c>
       <c r="H98" t="n">
-        <v>212899.530981</v>
+        <v>212895.898823</v>
       </c>
       <c r="I98" t="n">
-        <v>220242.314161</v>
+        <v>220232.95028</v>
       </c>
       <c r="J98" t="n">
         <v>248477.819588</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>231280.131933</v>
+        <v>231278.72655</v>
       </c>
       <c r="F99" t="n">
-        <v>260619.961021</v>
+        <v>260616.142807</v>
       </c>
       <c r="G99" t="n">
-        <v>309891.162657</v>
+        <v>309882.401937</v>
       </c>
       <c r="H99" t="n">
-        <v>361252.425207</v>
+        <v>361232.555641</v>
       </c>
       <c r="I99" t="n">
-        <v>407239.241849</v>
+        <v>407184.681373</v>
       </c>
       <c r="J99" t="n">
         <v>551577.409785</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>97566.139507</v>
+        <v>97565.305399</v>
       </c>
       <c r="F100" t="n">
-        <v>94523.42931000001</v>
+        <v>94521.418311</v>
       </c>
       <c r="G100" t="n">
-        <v>97573.84789999999</v>
+        <v>97569.71730600001</v>
       </c>
       <c r="H100" t="n">
-        <v>102741.66593</v>
+        <v>102733.014439</v>
       </c>
       <c r="I100" t="n">
-        <v>108515.697909</v>
+        <v>108493.132848</v>
       </c>
       <c r="J100" t="n">
         <v>155750.0857</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>231204.321248</v>
+        <v>231206.876456</v>
       </c>
       <c r="F101" t="n">
-        <v>239956.592009</v>
+        <v>239963.252608</v>
       </c>
       <c r="G101" t="n">
-        <v>262394.573913</v>
+        <v>262409.171804</v>
       </c>
       <c r="H101" t="n">
-        <v>286518.454562</v>
+        <v>286550.273484</v>
       </c>
       <c r="I101" t="n">
-        <v>307446.723529</v>
+        <v>307531.362588</v>
       </c>
       <c r="J101" t="n">
         <v>183418.360461</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1937915.766121</v>
+        <v>1937927.25</v>
       </c>
       <c r="F102" t="n">
-        <v>2129959.557746</v>
+        <v>2129991.686188</v>
       </c>
       <c r="G102" t="n">
-        <v>2494895.194149</v>
+        <v>2494971.614419</v>
       </c>
       <c r="H102" t="n">
-        <v>2901833.544449</v>
+        <v>2902012.631606</v>
       </c>
       <c r="I102" t="n">
-        <v>3288718.863126</v>
+        <v>3289224.829482</v>
       </c>
       <c r="J102" t="n">
         <v>2775216.558543</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2165295.595149</v>
+        <v>2165303.888359</v>
       </c>
       <c r="F103" t="n">
-        <v>2033503.241378</v>
+        <v>2033522.795555</v>
       </c>
       <c r="G103" t="n">
-        <v>2007265.336679</v>
+        <v>2007303.867167</v>
       </c>
       <c r="H103" t="n">
-        <v>2029322.400344</v>
+        <v>2029399.764164</v>
       </c>
       <c r="I103" t="n">
-        <v>2071095.817157</v>
+        <v>2071290.599745</v>
       </c>
       <c r="J103" t="n">
         <v>1834748.197196</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>174705.974689</v>
+        <v>174704.406006</v>
       </c>
       <c r="F104" t="n">
-        <v>185253.548543</v>
+        <v>185249.478661</v>
       </c>
       <c r="G104" t="n">
-        <v>208420.097952</v>
+        <v>208411.140613</v>
       </c>
       <c r="H104" t="n">
-        <v>236988.222403</v>
+        <v>236968.278646</v>
       </c>
       <c r="I104" t="n">
-        <v>265552.428071</v>
+        <v>265497.934884</v>
       </c>
       <c r="J104" t="n">
         <v>394513.484467</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>95097.747559</v>
+        <v>95097.24593600001</v>
       </c>
       <c r="F105" t="n">
-        <v>101715.405422</v>
+        <v>101714.092634</v>
       </c>
       <c r="G105" t="n">
-        <v>116703.568769</v>
+        <v>116700.631454</v>
       </c>
       <c r="H105" t="n">
-        <v>133171.843403</v>
+        <v>133165.270586</v>
       </c>
       <c r="I105" t="n">
-        <v>148541.93796</v>
+        <v>148523.969211</v>
       </c>
       <c r="J105" t="n">
         <v>196904.239561</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>949205.281138</v>
+        <v>949197.393451</v>
       </c>
       <c r="F106" t="n">
-        <v>1052662.064359</v>
+        <v>1052640.823524</v>
       </c>
       <c r="G106" t="n">
-        <v>1254941.064019</v>
+        <v>1254892.020082</v>
       </c>
       <c r="H106" t="n">
-        <v>1469541.801029</v>
+        <v>1469429.949336</v>
       </c>
       <c r="I106" t="n">
-        <v>1662093.817782</v>
+        <v>1661785.943503</v>
       </c>
       <c r="J106" t="n">
         <v>2402776.418202</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4509.521722</v>
+        <v>4508.738711</v>
       </c>
       <c r="F107" t="n">
-        <v>5289.019636</v>
+        <v>5286.749348</v>
       </c>
       <c r="G107" t="n">
-        <v>6219.322931</v>
+        <v>6214.048257</v>
       </c>
       <c r="H107" t="n">
-        <v>7247.811291</v>
+        <v>7235.738653</v>
       </c>
       <c r="I107" t="n">
-        <v>8482.200199999999</v>
+        <v>8448.436706</v>
       </c>
       <c r="J107" t="n">
         <v>72087.722939</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>371564.75328</v>
+        <v>371561.40298</v>
       </c>
       <c r="F108" t="n">
-        <v>392602.735863</v>
+        <v>392594.042246</v>
       </c>
       <c r="G108" t="n">
-        <v>431409.515622</v>
+        <v>431390.698637</v>
       </c>
       <c r="H108" t="n">
-        <v>473049.441544</v>
+        <v>473008.692415</v>
       </c>
       <c r="I108" t="n">
-        <v>511095.632789</v>
+        <v>510987.421729</v>
       </c>
       <c r="J108" t="n">
         <v>744268.240579</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>172855.892768</v>
+        <v>172856.199273</v>
       </c>
       <c r="F109" t="n">
-        <v>183653.297476</v>
+        <v>183654.166243</v>
       </c>
       <c r="G109" t="n">
-        <v>216245.755869</v>
+        <v>216247.958639</v>
       </c>
       <c r="H109" t="n">
-        <v>259835.002262</v>
+        <v>259840.616881</v>
       </c>
       <c r="I109" t="n">
-        <v>307841.038143</v>
+        <v>307858.323923</v>
       </c>
       <c r="J109" t="n">
         <v>326149.406892</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>545934.719325</v>
+        <v>545941.9133669999</v>
       </c>
       <c r="F110" t="n">
-        <v>611166.8032730001</v>
+        <v>611187.044001</v>
       </c>
       <c r="G110" t="n">
-        <v>726474.233855</v>
+        <v>726522.511614</v>
       </c>
       <c r="H110" t="n">
-        <v>846779.033235</v>
+        <v>846891.494742</v>
       </c>
       <c r="I110" t="n">
-        <v>951386.966993</v>
+        <v>951700.55801</v>
       </c>
       <c r="J110" t="n">
         <v>492565.829411</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>936056.564531</v>
+        <v>936054.899935</v>
       </c>
       <c r="F111" t="n">
-        <v>1021820.757661</v>
+        <v>1021816.613236</v>
       </c>
       <c r="G111" t="n">
-        <v>1170739.914262</v>
+        <v>1170731.231221</v>
       </c>
       <c r="H111" t="n">
-        <v>1328996.888133</v>
+        <v>1328978.449368</v>
       </c>
       <c r="I111" t="n">
-        <v>1479568.149694</v>
+        <v>1479519.493313</v>
       </c>
       <c r="J111" t="n">
         <v>1730418.192158</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1130392.463252</v>
+        <v>1130380.99297</v>
       </c>
       <c r="F112" t="n">
-        <v>1248471.719148</v>
+        <v>1248440.701375</v>
       </c>
       <c r="G112" t="n">
-        <v>1475631.515759</v>
+        <v>1475559.85096</v>
       </c>
       <c r="H112" t="n">
-        <v>1728459.075227</v>
+        <v>1728294.511214</v>
       </c>
       <c r="I112" t="n">
-        <v>1972651.120638</v>
+        <v>1972192.312405</v>
       </c>
       <c r="J112" t="n">
         <v>3068125.004517</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>119734.092168</v>
+        <v>119724.932997</v>
       </c>
       <c r="F113" t="n">
-        <v>123027.233761</v>
+        <v>123003.392446</v>
       </c>
       <c r="G113" t="n">
-        <v>116948.225633</v>
+        <v>116900.570676</v>
       </c>
       <c r="H113" t="n">
-        <v>118528.054623</v>
+        <v>118429.837775</v>
       </c>
       <c r="I113" t="n">
-        <v>127855.461244</v>
+        <v>127605.540523</v>
       </c>
       <c r="J113" t="n">
         <v>231744.606828</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21228.55735</v>
+        <v>21228.64451</v>
       </c>
       <c r="F114" t="n">
-        <v>30831.057332</v>
+        <v>30831.683511</v>
       </c>
       <c r="G114" t="n">
-        <v>43742.859859</v>
+        <v>43745.125661</v>
       </c>
       <c r="H114" t="n">
-        <v>57777.12478</v>
+        <v>57783.659229</v>
       </c>
       <c r="I114" t="n">
-        <v>69937.50477499999</v>
+        <v>69957.120734</v>
       </c>
       <c r="J114" t="n">
         <v>65843.308097</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>568495.984482</v>
+        <v>568505.056492</v>
       </c>
       <c r="F115" t="n">
-        <v>669807.215627</v>
+        <v>669830.430763</v>
       </c>
       <c r="G115" t="n">
-        <v>793580.702058</v>
+        <v>793626.091213</v>
       </c>
       <c r="H115" t="n">
-        <v>943715.7875569999</v>
+        <v>943807.469956</v>
       </c>
       <c r="I115" t="n">
-        <v>1099939.385341</v>
+        <v>1100169.690104</v>
       </c>
       <c r="J115" t="n">
         <v>1084481.069335</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>21237.413119</v>
+        <v>21237.526044</v>
       </c>
       <c r="F116" t="n">
-        <v>23287.197105</v>
+        <v>23287.485928</v>
       </c>
       <c r="G116" t="n">
-        <v>26514.682824</v>
+        <v>26515.299445</v>
       </c>
       <c r="H116" t="n">
-        <v>30512.285713</v>
+        <v>30513.629951</v>
       </c>
       <c r="I116" t="n">
-        <v>34190.094989</v>
+        <v>34193.647295</v>
       </c>
       <c r="J116" t="n">
         <v>31938.092586</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>56300.311798</v>
+        <v>56300.761492</v>
       </c>
       <c r="F117" t="n">
-        <v>74559.72371000001</v>
+        <v>74561.327663</v>
       </c>
       <c r="G117" t="n">
-        <v>91120.111481</v>
+        <v>91124.030694</v>
       </c>
       <c r="H117" t="n">
-        <v>107487.762541</v>
+        <v>107496.814272</v>
       </c>
       <c r="I117" t="n">
-        <v>120323.455075</v>
+        <v>120347.731587</v>
       </c>
       <c r="J117" t="n">
         <v>93786.814535</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>40536.034753</v>
+        <v>40534.736893</v>
       </c>
       <c r="F118" t="n">
-        <v>42629.869539</v>
+        <v>42626.509279</v>
       </c>
       <c r="G118" t="n">
-        <v>46114.193028</v>
+        <v>46107.02848</v>
       </c>
       <c r="H118" t="n">
-        <v>50886.068608</v>
+        <v>50870.591106</v>
       </c>
       <c r="I118" t="n">
-        <v>55766.341668</v>
+        <v>55726.033089</v>
       </c>
       <c r="J118" t="n">
         <v>117031.44932</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>20346.954525</v>
+        <v>20346.862582</v>
       </c>
       <c r="F119" t="n">
-        <v>25793.366495</v>
+        <v>25793.13966</v>
       </c>
       <c r="G119" t="n">
-        <v>33146.673657</v>
+        <v>33146.217192</v>
       </c>
       <c r="H119" t="n">
-        <v>41751.09527</v>
+        <v>41750.162568</v>
       </c>
       <c r="I119" t="n">
-        <v>49832.822139</v>
+        <v>49830.472038</v>
       </c>
       <c r="J119" t="n">
         <v>59748.313952</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>10817.347377</v>
+        <v>10817.444491</v>
       </c>
       <c r="F120" t="n">
-        <v>11938.83441</v>
+        <v>11939.088445</v>
       </c>
       <c r="G120" t="n">
-        <v>13699.20675</v>
+        <v>13699.760802</v>
       </c>
       <c r="H120" t="n">
-        <v>15910.061714</v>
+        <v>15911.292244</v>
       </c>
       <c r="I120" t="n">
-        <v>18013.337001</v>
+        <v>18016.642499</v>
       </c>
       <c r="J120" t="n">
         <v>14919.030572</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>135443.466545</v>
+        <v>135444.090599</v>
       </c>
       <c r="F121" t="n">
-        <v>169512.551654</v>
+        <v>169514.724507</v>
       </c>
       <c r="G121" t="n">
-        <v>214373.324372</v>
+        <v>214379.146313</v>
       </c>
       <c r="H121" t="n">
-        <v>262794.82895</v>
+        <v>262809.282783</v>
       </c>
       <c r="I121" t="n">
-        <v>302542.30776</v>
+        <v>302582.596961</v>
       </c>
       <c r="J121" t="n">
         <v>271001.078956</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>943264.9828840001</v>
+        <v>943265.088898</v>
       </c>
       <c r="F122" t="n">
-        <v>1047352.202626</v>
+        <v>1047351.470058</v>
       </c>
       <c r="G122" t="n">
-        <v>1215438.207878</v>
+        <v>1215434.917065</v>
       </c>
       <c r="H122" t="n">
-        <v>1435549.146894</v>
+        <v>1435539.476766</v>
       </c>
       <c r="I122" t="n">
-        <v>1663205.366159</v>
+        <v>1663176.60132</v>
       </c>
       <c r="J122" t="n">
         <v>1914102.828871</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>65697.933574</v>
+        <v>65721.243522</v>
       </c>
       <c r="F123" t="n">
-        <v>72921.39110199999</v>
+        <v>72982.09970200001</v>
       </c>
       <c r="G123" t="n">
-        <v>84357.292332</v>
+        <v>84488.24763500001</v>
       </c>
       <c r="H123" t="n">
-        <v>95469.677628</v>
+        <v>95745.50661900001</v>
       </c>
       <c r="I123" t="n">
-        <v>105000.497465</v>
+        <v>105685.165381</v>
       </c>
       <c r="J123" t="n">
         <v>37001.112152</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>501982.554566</v>
+        <v>502065.858765</v>
       </c>
       <c r="F124" t="n">
-        <v>557599.964577</v>
+        <v>557814.2893290001</v>
       </c>
       <c r="G124" t="n">
-        <v>635220.3257329999</v>
+        <v>635665.464133</v>
       </c>
       <c r="H124" t="n">
-        <v>711817.6167219999</v>
+        <v>712722.413395</v>
       </c>
       <c r="I124" t="n">
-        <v>781408.776303</v>
+        <v>783564.150431</v>
       </c>
       <c r="J124" t="n">
         <v>614613.816399</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>232538.35586</v>
+        <v>232431.741713</v>
       </c>
       <c r="F125" t="n">
-        <v>241091.489941</v>
+        <v>240816.456589</v>
       </c>
       <c r="G125" t="n">
-        <v>254893.600585</v>
+        <v>254317.506881</v>
       </c>
       <c r="H125" t="n">
-        <v>273998.48725</v>
+        <v>272817.861586</v>
       </c>
       <c r="I125" t="n">
-        <v>307505.210331</v>
+        <v>304665.168288</v>
       </c>
       <c r="J125" t="n">
         <v>656072.7887499999</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>449018.027993</v>
+        <v>449017.265847</v>
       </c>
       <c r="F130" t="n">
-        <v>521885.128647</v>
+        <v>521883.197511</v>
       </c>
       <c r="G130" t="n">
-        <v>671913.509205</v>
+        <v>671909.443917</v>
       </c>
       <c r="H130" t="n">
-        <v>899815.053942</v>
+        <v>899806.293054</v>
       </c>
       <c r="I130" t="n">
-        <v>1178844.959735</v>
+        <v>1178821.212038</v>
       </c>
       <c r="J130" t="n">
         <v>1524515.297578</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100353.615945</v>
+        <v>100353.865274</v>
       </c>
       <c r="F131" t="n">
-        <v>130237.938742</v>
+        <v>130238.812011</v>
       </c>
       <c r="G131" t="n">
-        <v>168174.836544</v>
+        <v>168177.268726</v>
       </c>
       <c r="H131" t="n">
-        <v>220143.813462</v>
+        <v>220150.524323</v>
       </c>
       <c r="I131" t="n">
-        <v>281289.315184</v>
+        <v>281311.082196</v>
       </c>
       <c r="J131" t="n">
         <v>154652.422207</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>989181.116911</v>
+        <v>989179.723824</v>
       </c>
       <c r="F132" t="n">
-        <v>1048447.169739</v>
+        <v>1048444.010135</v>
       </c>
       <c r="G132" t="n">
-        <v>1194405.515037</v>
+        <v>1194399.684649</v>
       </c>
       <c r="H132" t="n">
-        <v>1413422.120021</v>
+        <v>1413411.012841</v>
       </c>
       <c r="I132" t="n">
-        <v>1685110.976907</v>
+        <v>1685083.581863</v>
       </c>
       <c r="J132" t="n">
         <v>2018986.218551</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>242329.322841</v>
+        <v>242328.853808</v>
       </c>
       <c r="F133" t="n">
-        <v>383479.651544</v>
+        <v>383478.216964</v>
       </c>
       <c r="G133" t="n">
-        <v>627876.11008</v>
+        <v>627872.755157</v>
       </c>
       <c r="H133" t="n">
-        <v>957160.922943</v>
+        <v>957153.653027</v>
       </c>
       <c r="I133" t="n">
-        <v>1316487.888675</v>
+        <v>1316468.861231</v>
       </c>
       <c r="J133" t="n">
         <v>1662173.597279</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>226364.831777</v>
+        <v>226364.690294</v>
       </c>
       <c r="F134" t="n">
-        <v>223072.601089</v>
+        <v>223072.319481</v>
       </c>
       <c r="G134" t="n">
-        <v>244973.555159</v>
+        <v>244973.14249</v>
       </c>
       <c r="H134" t="n">
-        <v>290342.16574</v>
+        <v>290341.623432</v>
       </c>
       <c r="I134" t="n">
-        <v>351269.350805</v>
+        <v>351268.546357</v>
       </c>
       <c r="J134" t="n">
         <v>392044.791565</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>66985.462963</v>
+        <v>66985.51587</v>
       </c>
       <c r="F135" t="n">
-        <v>89770.985722</v>
+        <v>89771.219828</v>
       </c>
       <c r="G135" t="n">
-        <v>130554.091236</v>
+        <v>130554.957893</v>
       </c>
       <c r="H135" t="n">
-        <v>187561.500325</v>
+        <v>187564.395856</v>
       </c>
       <c r="I135" t="n">
-        <v>254936.551041</v>
+        <v>254947.048162</v>
       </c>
       <c r="J135" t="n">
         <v>216374.672367</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>240610.000634</v>
+        <v>240610.428308</v>
       </c>
       <c r="F136" t="n">
-        <v>239918.07162</v>
+        <v>239919.212769</v>
       </c>
       <c r="G136" t="n">
-        <v>248441.240363</v>
+        <v>248443.78316</v>
       </c>
       <c r="H136" t="n">
-        <v>267480.114893</v>
+        <v>267485.850885</v>
       </c>
       <c r="I136" t="n">
-        <v>303923.88089</v>
+        <v>303940.349717</v>
       </c>
       <c r="J136" t="n">
         <v>208194.864021</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>65724.096628</v>
+        <v>65723.972679</v>
       </c>
       <c r="F137" t="n">
-        <v>71842.547037</v>
+        <v>71842.25145500001</v>
       </c>
       <c r="G137" t="n">
-        <v>81057.683143</v>
+        <v>81057.109954</v>
       </c>
       <c r="H137" t="n">
-        <v>95553.172916</v>
+        <v>95552.008649</v>
       </c>
       <c r="I137" t="n">
-        <v>113506.370114</v>
+        <v>113503.336121</v>
       </c>
       <c r="J137" t="n">
         <v>142763.916593</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>115439.485433</v>
+        <v>115439.658407</v>
       </c>
       <c r="F138" t="n">
-        <v>124218.829635</v>
+        <v>124219.346084</v>
       </c>
       <c r="G138" t="n">
-        <v>144842.33232</v>
+        <v>144843.678277</v>
       </c>
       <c r="H138" t="n">
-        <v>173758.326646</v>
+        <v>173761.806978</v>
       </c>
       <c r="I138" t="n">
-        <v>204457.097507</v>
+        <v>204467.561928</v>
       </c>
       <c r="J138" t="n">
         <v>142336.184264</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>146177.326724</v>
+        <v>146177.938845</v>
       </c>
       <c r="F139" t="n">
-        <v>166353.053202</v>
+        <v>166354.858341</v>
       </c>
       <c r="G139" t="n">
-        <v>211350.226189</v>
+        <v>211355.017971</v>
       </c>
       <c r="H139" t="n">
-        <v>280290.80933</v>
+        <v>280303.920294</v>
       </c>
       <c r="I139" t="n">
-        <v>362295.686568</v>
+        <v>362338.298272</v>
       </c>
       <c r="J139" t="n">
         <v>88057.959523</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1269410.696804</v>
+        <v>1269413.170402</v>
       </c>
       <c r="F140" t="n">
-        <v>1261336.35748</v>
+        <v>1261342.903644</v>
       </c>
       <c r="G140" t="n">
-        <v>1406844.656746</v>
+        <v>1406860.484656</v>
       </c>
       <c r="H140" t="n">
-        <v>1707098.009533</v>
+        <v>1707138.85432</v>
       </c>
       <c r="I140" t="n">
-        <v>2118072.665071</v>
+        <v>2118202.168234</v>
       </c>
       <c r="J140" t="n">
         <v>1410610.668896</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>70092.852853</v>
+        <v>70092.419781</v>
       </c>
       <c r="F141" t="n">
-        <v>82220.08054700001</v>
+        <v>82218.878595</v>
       </c>
       <c r="G141" t="n">
-        <v>105560.807323</v>
+        <v>105557.91369</v>
       </c>
       <c r="H141" t="n">
-        <v>139288.826149</v>
+        <v>139281.652527</v>
       </c>
       <c r="I141" t="n">
-        <v>181117.246023</v>
+        <v>181095.479375</v>
       </c>
       <c r="J141" t="n">
         <v>370322.688007</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>20383.779494</v>
+        <v>20383.113658</v>
       </c>
       <c r="F142" t="n">
-        <v>36983.096886</v>
+        <v>36980.285072</v>
       </c>
       <c r="G142" t="n">
-        <v>76180.38905500001</v>
+        <v>76169.71186</v>
       </c>
       <c r="H142" t="n">
-        <v>141445.14</v>
+        <v>141408.379713</v>
       </c>
       <c r="I142" t="n">
-        <v>230324.673381</v>
+        <v>230189.136404</v>
       </c>
       <c r="J142" t="n">
         <v>1397484.248051</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4255.620973</v>
+        <v>4255.590023</v>
       </c>
       <c r="F146" t="n">
-        <v>4020.443245</v>
+        <v>4020.373847</v>
       </c>
       <c r="G146" t="n">
-        <v>4281.406592</v>
+        <v>4281.265972</v>
       </c>
       <c r="H146" t="n">
-        <v>5044.378917</v>
+        <v>5044.053649</v>
       </c>
       <c r="I146" t="n">
-        <v>6269.15655</v>
+        <v>6268.141744</v>
       </c>
       <c r="J146" t="n">
         <v>8439.928894999999</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>8331.366689</v>
+        <v>8331.253647</v>
       </c>
       <c r="F147" t="n">
-        <v>9059.111826</v>
+        <v>9058.802798000001</v>
       </c>
       <c r="G147" t="n">
-        <v>10639.926786</v>
+        <v>10639.20357</v>
       </c>
       <c r="H147" t="n">
-        <v>13016.034349</v>
+        <v>13014.27495</v>
       </c>
       <c r="I147" t="n">
-        <v>16218.220608</v>
+        <v>16212.786474</v>
       </c>
       <c r="J147" t="n">
         <v>24123.802538</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>468684.846138</v>
+        <v>468684.99013</v>
       </c>
       <c r="F148" t="n">
-        <v>537588.764804</v>
+        <v>537589.14323</v>
       </c>
       <c r="G148" t="n">
-        <v>684693.558617</v>
+        <v>684694.422453</v>
       </c>
       <c r="H148" t="n">
-        <v>893874.729419</v>
+        <v>893876.814086</v>
       </c>
       <c r="I148" t="n">
-        <v>1152051.250927</v>
+        <v>1152057.699867</v>
       </c>
       <c r="J148" t="n">
         <v>1364373.799652</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>31439.254173</v>
+        <v>31438.962808</v>
       </c>
       <c r="F149" t="n">
-        <v>36362.176081</v>
+        <v>36361.35765</v>
       </c>
       <c r="G149" t="n">
-        <v>46497.046082</v>
+        <v>46494.940022</v>
       </c>
       <c r="H149" t="n">
-        <v>60530.963719</v>
+        <v>60525.35288</v>
       </c>
       <c r="I149" t="n">
-        <v>76776.14492999999</v>
+        <v>76757.949431</v>
       </c>
       <c r="J149" t="n">
         <v>143014.024147</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>262321.270366</v>
+        <v>262321.409898</v>
       </c>
       <c r="F150" t="n">
-        <v>297388.717566</v>
+        <v>297389.307335</v>
       </c>
       <c r="G150" t="n">
-        <v>376066.136766</v>
+        <v>376067.499346</v>
       </c>
       <c r="H150" t="n">
-        <v>474717.440677</v>
+        <v>474719.763591</v>
       </c>
       <c r="I150" t="n">
-        <v>571236.471177</v>
+        <v>571239.085592</v>
       </c>
       <c r="J150" t="n">
         <v>654893.9929440001</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>90275.023693</v>
+        <v>90274.501613</v>
       </c>
       <c r="F151" t="n">
-        <v>110398.865038</v>
+        <v>110397.336325</v>
       </c>
       <c r="G151" t="n">
-        <v>148926.666965</v>
+        <v>148922.484187</v>
       </c>
       <c r="H151" t="n">
-        <v>196900.695954</v>
+        <v>196889.186481</v>
       </c>
       <c r="I151" t="n">
-        <v>244846.015215</v>
+        <v>244808.720426</v>
       </c>
       <c r="J151" t="n">
         <v>386006.425233</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>167436.83018</v>
+        <v>167434.385081</v>
       </c>
       <c r="F152" t="n">
-        <v>208055.735882</v>
+        <v>208048.257907</v>
       </c>
       <c r="G152" t="n">
-        <v>267368.724881</v>
+        <v>267349.424094</v>
       </c>
       <c r="H152" t="n">
-        <v>333620.73338</v>
+        <v>333571.958708</v>
       </c>
       <c r="I152" t="n">
-        <v>394986.04306</v>
+        <v>394840.540615</v>
       </c>
       <c r="J152" t="n">
         <v>807350.8370009999</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>193846.80234</v>
+        <v>193849.946891</v>
       </c>
       <c r="F153" t="n">
-        <v>225038.955921</v>
+        <v>225048.234293</v>
       </c>
       <c r="G153" t="n">
-        <v>296626.952075</v>
+        <v>296651.316626</v>
       </c>
       <c r="H153" t="n">
-        <v>396210.798995</v>
+        <v>396274.918193</v>
       </c>
       <c r="I153" t="n">
-        <v>507783.767237</v>
+        <v>507984.481186</v>
       </c>
       <c r="J153" t="n">
         <v>96302.556052</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>47756.079248</v>
+        <v>47756.053707</v>
       </c>
       <c r="F154" t="n">
-        <v>57890.619672</v>
+        <v>57890.576651</v>
       </c>
       <c r="G154" t="n">
-        <v>73637.150352</v>
+        <v>73637.012845</v>
       </c>
       <c r="H154" t="n">
-        <v>90354.628296</v>
+        <v>90354.081168</v>
       </c>
       <c r="I154" t="n">
-        <v>104124.433601</v>
+        <v>104122.09797</v>
       </c>
       <c r="J154" t="n">
         <v>120976.077843</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>64576.994755</v>
+        <v>64580.402298</v>
       </c>
       <c r="F155" t="n">
-        <v>102303.068042</v>
+        <v>102316.416908</v>
       </c>
       <c r="G155" t="n">
-        <v>161688.130978</v>
+        <v>161729.728171</v>
       </c>
       <c r="H155" t="n">
-        <v>246153.874525</v>
+        <v>246278.836156</v>
       </c>
       <c r="I155" t="n">
-        <v>349932.555541</v>
+        <v>350369.877127</v>
       </c>
       <c r="J155" t="n">
         <v>196110.478887</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>224956.771092</v>
+        <v>224958.378964</v>
       </c>
       <c r="F156" t="n">
-        <v>339285.648623</v>
+        <v>339290.796004</v>
       </c>
       <c r="G156" t="n">
-        <v>507986.437601</v>
+        <v>507998.98586</v>
       </c>
       <c r="H156" t="n">
-        <v>725412.738208</v>
+        <v>725441.239357</v>
       </c>
       <c r="I156" t="n">
-        <v>964440.686585</v>
+        <v>964513.6357</v>
       </c>
       <c r="J156" t="n">
         <v>1204368.240045</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1440.538996</v>
+        <v>1440.277768</v>
       </c>
       <c r="F157" t="n">
-        <v>2746.146417</v>
+        <v>2744.853156</v>
       </c>
       <c r="G157" t="n">
-        <v>5022.889423</v>
+        <v>5018.014936</v>
       </c>
       <c r="H157" t="n">
-        <v>8087.279883</v>
+        <v>8071.341831</v>
       </c>
       <c r="I157" t="n">
-        <v>11294.08262</v>
+        <v>11239.007904</v>
       </c>
       <c r="J157" t="n">
         <v>48330.09509</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>50160.005283</v>
+        <v>50157.172302</v>
       </c>
       <c r="F158" t="n">
-        <v>66652.807608</v>
+        <v>66643.323448</v>
       </c>
       <c r="G158" t="n">
-        <v>87586.61842</v>
+        <v>87561.58612399999</v>
       </c>
       <c r="H158" t="n">
-        <v>114035.335768</v>
+        <v>113969.727185</v>
       </c>
       <c r="I158" t="n">
-        <v>143632.740988</v>
+        <v>143425.875105</v>
       </c>
       <c r="J158" t="n">
         <v>302835.116948</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>612.399673</v>
+        <v>612.317624</v>
       </c>
       <c r="F159" t="n">
-        <v>884.538024</v>
+        <v>884.238997</v>
       </c>
       <c r="G159" t="n">
-        <v>1288.04131</v>
+        <v>1287.163386</v>
       </c>
       <c r="H159" t="n">
-        <v>1794.967221</v>
+        <v>1792.509848</v>
       </c>
       <c r="I159" t="n">
-        <v>2356.482147</v>
+        <v>2348.486196</v>
       </c>
       <c r="J159" t="n">
         <v>7789.714264</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>13144.445202</v>
+        <v>13142.606045</v>
       </c>
       <c r="F160" t="n">
-        <v>20821.959647</v>
+        <v>20814.539847</v>
       </c>
       <c r="G160" t="n">
-        <v>32337.821697</v>
+        <v>32314.460953</v>
       </c>
       <c r="H160" t="n">
-        <v>47666.788124</v>
+        <v>47597.329353</v>
       </c>
       <c r="I160" t="n">
-        <v>66295.273849</v>
+        <v>66054.939698</v>
       </c>
       <c r="J160" t="n">
         <v>246781.683497</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>14850.935871</v>
+        <v>14850.886846</v>
       </c>
       <c r="F162" t="n">
-        <v>12429.512652</v>
+        <v>12429.347586</v>
       </c>
       <c r="G162" t="n">
-        <v>10840.764572</v>
+        <v>10840.381817</v>
       </c>
       <c r="H162" t="n">
-        <v>10768.647715</v>
+        <v>10767.771992</v>
       </c>
       <c r="I162" t="n">
-        <v>11627.019939</v>
+        <v>11624.554194</v>
       </c>
       <c r="J162" t="n">
         <v>14634.278166</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1507.359221</v>
+        <v>1507.148166</v>
       </c>
       <c r="F163" t="n">
-        <v>2066.622605</v>
+        <v>2065.903549</v>
       </c>
       <c r="G163" t="n">
-        <v>2913.913746</v>
+        <v>2911.907402</v>
       </c>
       <c r="H163" t="n">
-        <v>3970.906015</v>
+        <v>3965.524798</v>
       </c>
       <c r="I163" t="n">
-        <v>5135.903502</v>
+        <v>5119.169178</v>
       </c>
       <c r="J163" t="n">
         <v>18355.661202</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>16384.936388</v>
+        <v>16383.367207</v>
       </c>
       <c r="F164" t="n">
-        <v>24620.659185</v>
+        <v>24614.804738</v>
       </c>
       <c r="G164" t="n">
-        <v>36860.606422</v>
+        <v>36843.251607</v>
       </c>
       <c r="H164" t="n">
-        <v>53453.201105</v>
+        <v>53403.650701</v>
       </c>
       <c r="I164" t="n">
-        <v>73489.11685999999</v>
+        <v>73324.846133</v>
       </c>
       <c r="J164" t="n">
         <v>220655.478779</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>57628.397436</v>
+        <v>57630.634543</v>
       </c>
       <c r="F165" t="n">
-        <v>75667.46322600001</v>
+        <v>75674.56928</v>
       </c>
       <c r="G165" t="n">
-        <v>88818.121012</v>
+        <v>88834.257694</v>
       </c>
       <c r="H165" t="n">
-        <v>105716.578898</v>
+        <v>105754.052276</v>
       </c>
       <c r="I165" t="n">
-        <v>125052.301045</v>
+        <v>125160.788087</v>
       </c>
       <c r="J165" t="n">
         <v>65700.172095</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>57219.026152</v>
+        <v>57217.225734</v>
       </c>
       <c r="F166" t="n">
-        <v>71134.597754</v>
+        <v>71128.866868</v>
       </c>
       <c r="G166" t="n">
-        <v>87678.392939</v>
+        <v>87664.006184</v>
       </c>
       <c r="H166" t="n">
-        <v>109156.53182</v>
+        <v>109120.567282</v>
       </c>
       <c r="I166" t="n">
-        <v>132282.396056</v>
+        <v>132175.616368</v>
       </c>
       <c r="J166" t="n">
         <v>228724.851769</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>530723.018882</v>
+        <v>530733.740386</v>
       </c>
       <c r="F167" t="n">
-        <v>630711.370525</v>
+        <v>630741.186733</v>
       </c>
       <c r="G167" t="n">
-        <v>761661.286368</v>
+        <v>761729.0109690001</v>
       </c>
       <c r="H167" t="n">
-        <v>961728.53202</v>
+        <v>961892.59328</v>
       </c>
       <c r="I167" t="n">
-        <v>1207073.816476</v>
+        <v>1207574.467644</v>
       </c>
       <c r="J167" t="n">
         <v>1073136.362531</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>455.448869</v>
+        <v>455.358279</v>
       </c>
       <c r="F168" t="n">
-        <v>596.799942</v>
+        <v>596.504637</v>
       </c>
       <c r="G168" t="n">
-        <v>776.7336319999999</v>
+        <v>775.9711119999999</v>
       </c>
       <c r="H168" t="n">
-        <v>1022.674342</v>
+        <v>1020.698743</v>
       </c>
       <c r="I168" t="n">
-        <v>1332.327456</v>
+        <v>1326.177028</v>
       </c>
       <c r="J168" t="n">
         <v>6283.047267</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>291439.155973</v>
+        <v>291435.452269</v>
       </c>
       <c r="F169" t="n">
-        <v>375896.61577</v>
+        <v>375883.764226</v>
       </c>
       <c r="G169" t="n">
-        <v>479912.449827</v>
+        <v>479877.666064</v>
       </c>
       <c r="H169" t="n">
-        <v>633079.473312</v>
+        <v>632985.517082</v>
       </c>
       <c r="I169" t="n">
-        <v>833228.185164</v>
+        <v>832924.264994</v>
       </c>
       <c r="J169" t="n">
         <v>1291499.253353</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>12718.784775</v>
+        <v>12717.651713</v>
       </c>
       <c r="F170" t="n">
-        <v>19959.381206</v>
+        <v>19954.965043</v>
       </c>
       <c r="G170" t="n">
-        <v>29389.511876</v>
+        <v>29376.588616</v>
       </c>
       <c r="H170" t="n">
-        <v>41030.004427</v>
+        <v>40994.310933</v>
       </c>
       <c r="I170" t="n">
-        <v>54066.758402</v>
+        <v>53952.757404</v>
       </c>
       <c r="J170" t="n">
         <v>152115.957475</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>67343.215624</v>
+        <v>67336.62139099999</v>
       </c>
       <c r="F171" t="n">
-        <v>83782.872536</v>
+        <v>83762.32900500001</v>
       </c>
       <c r="G171" t="n">
-        <v>103645.64429</v>
+        <v>103594.883127</v>
       </c>
       <c r="H171" t="n">
-        <v>129300.073609</v>
+        <v>129174.586296</v>
       </c>
       <c r="I171" t="n">
-        <v>158070.145414</v>
+        <v>157698.604607</v>
       </c>
       <c r="J171" t="n">
         <v>449841.260123</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>178337.586875</v>
+        <v>178330.871855</v>
       </c>
       <c r="F172" t="n">
-        <v>208015.738414</v>
+        <v>207995.64943</v>
       </c>
       <c r="G172" t="n">
-        <v>232835.717707</v>
+        <v>232789.673838</v>
       </c>
       <c r="H172" t="n">
-        <v>265711.570649</v>
+        <v>265605.391979</v>
       </c>
       <c r="I172" t="n">
-        <v>305413.213889</v>
+        <v>305112.709369</v>
       </c>
       <c r="J172" t="n">
         <v>550189.233176</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1012.459604</v>
+        <v>1012.415593</v>
       </c>
       <c r="F173" t="n">
-        <v>1523.524458</v>
+        <v>1523.35791</v>
       </c>
       <c r="G173" t="n">
-        <v>2180.816625</v>
+        <v>2180.337494</v>
       </c>
       <c r="H173" t="n">
-        <v>2994.643085</v>
+        <v>2993.330607</v>
       </c>
       <c r="I173" t="n">
-        <v>3942.843014</v>
+        <v>3938.623585</v>
       </c>
       <c r="J173" t="n">
         <v>8117.310213</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>619174.521933</v>
+        <v>619172.855192</v>
       </c>
       <c r="F174" t="n">
-        <v>733312.876332</v>
+        <v>733305.9201090001</v>
       </c>
       <c r="G174" t="n">
-        <v>868956.531018</v>
+        <v>868935.950559</v>
       </c>
       <c r="H174" t="n">
-        <v>1062637.333012</v>
+        <v>1062581.594226</v>
       </c>
       <c r="I174" t="n">
-        <v>1289953.497786</v>
+        <v>1289782.980808</v>
       </c>
       <c r="J174" t="n">
         <v>1648178.332285</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2090.101421</v>
+        <v>2090.08965</v>
       </c>
       <c r="F175" t="n">
-        <v>3824.034608</v>
+        <v>3823.978409</v>
       </c>
       <c r="G175" t="n">
-        <v>6675.904096</v>
+        <v>6675.700676</v>
       </c>
       <c r="H175" t="n">
-        <v>10882.215785</v>
+        <v>10881.551124</v>
       </c>
       <c r="I175" t="n">
-        <v>16389.571551</v>
+        <v>16387.192824</v>
       </c>
       <c r="J175" t="n">
         <v>24407.799043</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>179.226219</v>
+        <v>179.176416</v>
       </c>
       <c r="F176" t="n">
-        <v>201.602261</v>
+        <v>201.462686</v>
       </c>
       <c r="G176" t="n">
-        <v>233.558709</v>
+        <v>233.238045</v>
       </c>
       <c r="H176" t="n">
-        <v>283.45864</v>
+        <v>282.694969</v>
       </c>
       <c r="I176" t="n">
-        <v>349.913177</v>
+        <v>347.68182</v>
       </c>
       <c r="J176" t="n">
         <v>1999.95471</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>572394.799942</v>
+        <v>572405.66672</v>
       </c>
       <c r="F177" t="n">
-        <v>915499.197649</v>
+        <v>915540.868606</v>
       </c>
       <c r="G177" t="n">
-        <v>1360230.888823</v>
+        <v>1360349.586686</v>
       </c>
       <c r="H177" t="n">
-        <v>1868953.978273</v>
+        <v>1869270.030509</v>
       </c>
       <c r="I177" t="n">
-        <v>2349767.59036</v>
+        <v>2350736.669461</v>
       </c>
       <c r="J177" t="n">
         <v>2017864.82817</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>449.772971</v>
+        <v>449.661159</v>
       </c>
       <c r="F178" t="n">
-        <v>621.6451039999999</v>
+        <v>621.261733</v>
       </c>
       <c r="G178" t="n">
-        <v>830.413078</v>
+        <v>829.399128</v>
       </c>
       <c r="H178" t="n">
-        <v>1113.234815</v>
+        <v>1110.566324</v>
       </c>
       <c r="I178" t="n">
-        <v>1476.122189</v>
+        <v>1467.716329</v>
       </c>
       <c r="J178" t="n">
         <v>8239.930388000001</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>311.351845</v>
+        <v>311.276882</v>
       </c>
       <c r="F179" t="n">
-        <v>378.165973</v>
+        <v>377.939653</v>
       </c>
       <c r="G179" t="n">
-        <v>469.534159</v>
+        <v>468.977882</v>
       </c>
       <c r="H179" t="n">
-        <v>591.678578</v>
+        <v>590.3029780000001</v>
       </c>
       <c r="I179" t="n">
-        <v>741.8868210000001</v>
+        <v>737.789269</v>
       </c>
       <c r="J179" t="n">
         <v>3834.808353</v>
@@ -14130,19 +14130,19 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="F181" t="n">
         <v>-1e-06</v>
       </c>
-      <c r="F181" t="n">
-        <v>-1.2e-05</v>
-      </c>
       <c r="G181" t="n">
-        <v>3e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="H181" t="n">
-        <v>4e-06</v>
+        <v>6e-06</v>
       </c>
       <c r="I181" t="n">
-        <v>3e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="J181" t="n">
         <v>-3e-06</v>
